--- a/source/connector.xlsx
+++ b/source/connector.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\enterprise\omega\Папки отделов\Департамент закупівель та логістики\Відділ реінжинірингу процесів закупівель\Master data\З'єднувач\обработка\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\enterprise\services\rdsdir\omelyanenko genadiy\Desktop\Trash\images 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D06C79-C076-43E0-8F88-EC987188A017}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF1DFFEF-7D09-472A-B32C-34AA70872B9D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12070,7 +12070,7 @@
     <t>Родитель</t>
   </si>
   <si>
-    <t>Пневматические фитирнги</t>
+    <t>Пневматические фитинги</t>
   </si>
 </sst>
 </file>
